--- a/Config/Excel/__tables__.xlsx
+++ b/Config/Excel/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="9435"/>
+    <workbookView windowWidth="28560" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -174,6 +174,24 @@
   </si>
   <si>
     <t>Tables/Unit表.xlsx</t>
+  </si>
+  <si>
+    <t>TbMonster</t>
+  </si>
+  <si>
+    <t>MonsterTable</t>
+  </si>
+  <si>
+    <t>Tables/怪物表.xlsx</t>
+  </si>
+  <si>
+    <t>TbRole</t>
+  </si>
+  <si>
+    <t>RoleTable</t>
+  </si>
+  <si>
+    <t>Tables/角色表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
@@ -1316,6 +1334,34 @@
         <v>48</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Excel/__tables__.xlsx
+++ b/Config/Excel/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28560" windowHeight="4560"/>
+    <workbookView windowWidth="17640" windowHeight="8340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -192,6 +192,24 @@
   </si>
   <si>
     <t>Tables/角色表.xlsx</t>
+  </si>
+  <si>
+    <t>TbSkill</t>
+  </si>
+  <si>
+    <t>SkillTable</t>
+  </si>
+  <si>
+    <t>Tables/技能配置表.xlsx</t>
+  </si>
+  <si>
+    <t>TbRoleSkillSet</t>
+  </si>
+  <si>
+    <t>RoleSkillSetTable</t>
+  </si>
+  <si>
+    <t>Tables/角色技能组表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
@@ -1362,6 +1380,34 @@
         <v>54</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
